--- a/new-info45/web.xlsx
+++ b/new-info45/web.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="39">
   <si>
     <t>domain</t>
   </si>
@@ -46,16 +46,34 @@
     <t>json</t>
   </si>
   <si>
-    <t>read.mousseline.cloud</t>
-  </si>
-  <si>
-    <t>#ae1c31</t>
-  </si>
-  <si>
-    <t>sec.mousseline.cloud</t>
-  </si>
-  <si>
-    <t>pink</t>
+    <t>sec.fulgent.site</t>
+  </si>
+  <si>
+    <t>#ddd23b</t>
+  </si>
+  <si>
+    <t>read.plisse.cloud</t>
+  </si>
+  <si>
+    <t>#ba8677</t>
+  </si>
+  <si>
+    <t>sec.plisse.cloud</t>
+  </si>
+  <si>
+    <t>#1c579b</t>
+  </si>
+  <si>
+    <t>spiraling.cloud</t>
+  </si>
+  <si>
+    <t>#24a765</t>
+  </si>
+  <si>
+    <t>silvanium.cloud</t>
+  </si>
+  <si>
+    <t>#284fef</t>
   </si>
   <si>
     <t>color</t>
@@ -140,7 +158,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -185,8 +203,17 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10.5"/>
-      <color rgb="FFFBF1D7"/>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF2972F4"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -343,7 +370,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="48">
+  <fills count="52">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -436,7 +463,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAE1C31"/>
+        <fgColor rgb="FFDDD23B"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA8677"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C579B"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24A765"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF284FEF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -736,152 +787,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -934,14 +985,29 @@
     <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1364,10 +1430,10 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="21" t="s">
         <v>8</v>
       </c>
       <c r="D3">
@@ -1378,21 +1444,33 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="20"/>
-      <c r="B4" s="13"/>
+      <c r="A4" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="6"/>
-      <c r="B5" s="14"/>
+      <c r="A5" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="24" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="20"/>
-      <c r="B6" s="15"/>
+      <c r="A6" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>14</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" display="read.mousseline.cloud"/>
-    <hyperlink ref="A3" r:id="rId1" display="sec.mousseline.cloud"/>
+    <hyperlink ref="A3" r:id="rId1" display="read.plisse.cloud"/>
+    <hyperlink ref="A4" r:id="rId1" display="sec.plisse.cloud"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1413,7 +1491,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -1427,10 +1505,10 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1441,10 +1519,10 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1455,10 +1533,10 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1469,10 +1547,10 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1483,10 +1561,10 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1497,18 +1575,18 @@
     </row>
     <row r="16" spans="1:7">
       <c r="F16" s="16" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="6:7">
       <c r="F17" s="16" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1548,49 +1626,49 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E3" s="6"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>

--- a/new-info45/web.xlsx
+++ b/new-info45/web.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="35">
   <si>
     <t>domain</t>
   </si>
@@ -46,34 +46,22 @@
     <t>json</t>
   </si>
   <si>
-    <t>sec.fulgent.site</t>
-  </si>
-  <si>
-    <t>#ddd23b</t>
-  </si>
-  <si>
-    <t>read.plisse.cloud</t>
-  </si>
-  <si>
-    <t>#ba8677</t>
-  </si>
-  <si>
-    <t>sec.plisse.cloud</t>
-  </si>
-  <si>
-    <t>#1c579b</t>
-  </si>
-  <si>
-    <t>spiraling.cloud</t>
-  </si>
-  <si>
-    <t>#24a765</t>
-  </si>
-  <si>
-    <t>silvanium.cloud</t>
-  </si>
-  <si>
-    <t>#284fef</t>
+    <t>duskthorn.cloud</t>
+  </si>
+  <si>
+    <t>#606da1</t>
+  </si>
+  <si>
+    <t>read.duskthorn.cloud</t>
+  </si>
+  <si>
+    <t>#718771</t>
+  </si>
+  <si>
+    <t>sec.duskthorn.cloud</t>
+  </si>
+  <si>
+    <t>#73AE52</t>
   </si>
   <si>
     <t>color</t>
@@ -158,7 +146,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -203,9 +191,15 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFFBF1D7"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -463,19 +457,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDD23B"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA8677"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C579B"/>
+        <fgColor rgb="FF606DA1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF718771"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF73AE52"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -787,148 +781,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -988,19 +982,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1452,26 +1446,14 @@
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>12</v>
-      </c>
+      <c r="A5" s="23"/>
+      <c r="B5" s="24"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="25" t="s">
-        <v>14</v>
-      </c>
+      <c r="A6" s="23"/>
+      <c r="B6" s="25"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A3" r:id="rId1" display="read.plisse.cloud"/>
-    <hyperlink ref="A4" r:id="rId1" display="sec.plisse.cloud"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -1491,7 +1473,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -1505,10 +1487,10 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1519,10 +1501,10 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1533,10 +1515,10 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1547,10 +1529,10 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1561,10 +1543,10 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1575,18 +1557,18 @@
     </row>
     <row r="16" spans="1:7">
       <c r="F16" s="16" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="6:7">
       <c r="F17" s="16" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1626,49 +1608,49 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E3" s="6"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>

--- a/new-info45/web.xlsx
+++ b/new-info45/web.xlsx
@@ -4,12 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="14475" windowHeight="8505"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="13" r:id="rId1"/>
-    <sheet name="Sheet3" sheetId="14" r:id="rId2"/>
-    <sheet name="Sheet5" sheetId="10" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="14" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="13" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="15" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="16" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,111 +30,105 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
   <si>
     <t>domain</t>
   </si>
   <si>
+    <t>color</t>
+  </si>
+  <si>
+    <t>color2</t>
+  </si>
+  <si>
+    <t>amortization.site</t>
+  </si>
+  <si>
+    <t>#ffd9a3</t>
+  </si>
+  <si>
+    <t>krakenbane.com</t>
+  </si>
+  <si>
+    <t>#f597ba</t>
+  </si>
+  <si>
     <t>color1</t>
   </si>
   <si>
-    <t>color2</t>
-  </si>
-  <si>
     <t>info</t>
   </si>
   <si>
     <t>json</t>
   </si>
   <si>
-    <t>duskthorn.cloud</t>
-  </si>
-  <si>
-    <t>#606da1</t>
-  </si>
-  <si>
-    <t>read.duskthorn.cloud</t>
-  </si>
-  <si>
-    <t>#718771</t>
-  </si>
-  <si>
-    <t>sec.duskthorn.cloud</t>
-  </si>
-  <si>
-    <t>#73AE52</t>
-  </si>
-  <si>
-    <t>color</t>
-  </si>
-  <si>
-    <t>vernations.cloud</t>
-  </si>
-  <si>
-    <t>#ffa500</t>
-  </si>
-  <si>
-    <t>mizars.cloud</t>
-  </si>
-  <si>
-    <t>#9d4edd</t>
-  </si>
-  <si>
-    <t>hortus.cloud</t>
-  </si>
-  <si>
-    <t>#64ffda</t>
-  </si>
-  <si>
-    <t>cruppers.top</t>
-  </si>
-  <si>
-    <t>#e63946</t>
-  </si>
-  <si>
-    <t>secateurs.top</t>
-  </si>
-  <si>
-    <t>#c9a87a</t>
-  </si>
-  <si>
-    <t>spuddles.fun</t>
-  </si>
-  <si>
-    <t>#707899</t>
-  </si>
-  <si>
-    <t>moilfuns.fun</t>
-  </si>
-  <si>
-    <t>#70c588</t>
-  </si>
-  <si>
-    <t>conatuss.top</t>
-  </si>
-  <si>
-    <t>#e2e1dd</t>
-  </si>
-  <si>
-    <t>#8abe98</t>
-  </si>
-  <si>
-    <t>droshky.fun</t>
-  </si>
-  <si>
-    <t>#fafbe6</t>
-  </si>
-  <si>
-    <t>#a48ce6</t>
-  </si>
-  <si>
-    <t>#c6e6e8</t>
-  </si>
-  <si>
-    <t>#373834</t>
-  </si>
-  <si>
-    <t>#e3e3e5</t>
+    <t>draconic.cloud</t>
+  </si>
+  <si>
+    <t>#e4c6d0</t>
+  </si>
+  <si>
+    <t>#425066</t>
+  </si>
+  <si>
+    <t>umbrage.cloud</t>
+  </si>
+  <si>
+    <t>#a2e2c6</t>
+  </si>
+  <si>
+    <t>#012896</t>
+  </si>
+  <si>
+    <t>haberdasher.cloud</t>
+  </si>
+  <si>
+    <t>#fb9966</t>
+  </si>
+  <si>
+    <t>melancholy.cloud</t>
+  </si>
+  <si>
+    <t>#afcd53</t>
+  </si>
+  <si>
+    <t>insulary.fun</t>
+  </si>
+  <si>
+    <t>#ed6d46</t>
+  </si>
+  <si>
+    <t>vapourous.fun</t>
+  </si>
+  <si>
+    <t>#7d929f</t>
+  </si>
+  <si>
+    <t>unsdgaction.com</t>
+  </si>
+  <si>
+    <t>#ddbb99</t>
+  </si>
+  <si>
+    <t>周一</t>
+  </si>
+  <si>
+    <t>周二</t>
+  </si>
+  <si>
+    <t>周三</t>
+  </si>
+  <si>
+    <t>周四</t>
+  </si>
+  <si>
+    <t>周五</t>
+  </si>
+  <si>
+    <t>周六</t>
+  </si>
+  <si>
+    <t>周日</t>
   </si>
 </sst>
 </file>
@@ -155,9 +150,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="9"/>
-      <color rgb="FF0000FF"/>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -170,13 +165,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10.5"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
@@ -185,23 +173,10 @@
     </font>
     <font>
       <u/>
-      <sz val="10"/>
-      <color rgb="FF1450B8"/>
-      <name val="Helvetica"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FFFBF1D7"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -214,17 +189,39 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF2972F4"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -364,7 +361,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="52">
+  <fills count="45">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -373,115 +370,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2E1DD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ABE98"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAFBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA48CE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E6E8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF373834"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3E3E5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF707899"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFA500"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9D4EDD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF64FFDA"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE63946"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9A87A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF70C588"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF606DA1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF718771"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF73AE52"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24A765"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF284FEF"/>
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFB9966"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFCD53"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED6D46"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7D929F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDBB99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4C6D0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF425066"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2E2C6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF012896"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFD9A3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF597BA"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -672,12 +627,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -781,28 +751,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -814,194 +784,186 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1056,6 +1018,11 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <colors>
+    <mruColors>
+      <color rgb="00F4F207"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1386,13 +1353,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5" outlineLevelCol="4"/>
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="17.875" customWidth="1"/>
+    <col min="1" max="1" width="27.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1402,58 +1369,195 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B2" s="16" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="18" t="s">
+      <c r="C2" s="12"/>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B3" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="22" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="23"/>
-      <c r="B5" s="24"/>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="23"/>
-      <c r="B6" s="25"/>
+      <c r="C3" s="12"/>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="20"/>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="21"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="20"/>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="21"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="15"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="22"/>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="23"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="22"/>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="22"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="22"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="22"/>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="22"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="22"/>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="22"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="22"/>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="22"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="22"/>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="22"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="22"/>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="22"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="22"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="22"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="22"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="22"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="22"/>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="22"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="D21" s="22"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F16" r:id="rId1"/>
+    <hyperlink ref="F17" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -1462,125 +1566,106 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="27.75" customWidth="1"/>
+    <col min="1" max="1" width="26.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="3">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E2" s="3">
+        <v>6</v>
+      </c>
+      <c r="F2" s="3"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="3">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="F16" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="6:7">
-      <c r="F17" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="G17" s="17" t="s">
-        <v>25</v>
-      </c>
+      <c r="E3" s="3">
+        <v>6</v>
+      </c>
+      <c r="F3" s="3"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="15"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="3"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="15"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="3"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="15"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="3"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="15"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="15"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="3"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="F16" r:id="rId1" display="spuddles.fun"/>
-    <hyperlink ref="F17" r:id="rId2" display="moilfuns.fun"/>
-    <hyperlink ref="A2" r:id="rId3" display="vernations.cloud"/>
-    <hyperlink ref="A3" r:id="rId4" display="mizars.cloud"/>
-    <hyperlink ref="A4" r:id="rId5" display="hortus.cloud"/>
-    <hyperlink ref="A5" r:id="rId6" display="cruppers.top"/>
-    <hyperlink ref="A6" r:id="rId7" display="secateurs.top"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -1592,7 +1677,7 @@
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="1" max="1" width="15.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1600,76 +1685,131 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>28</v>
+      <c r="A2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" s="6"/>
+      <c r="A3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>14</v>
+      </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="1" t="s">
+      <c r="B5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
+      <c r="B6" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>14</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A6" r:id="rId1"/>
-    <hyperlink ref="A2" r:id="rId2" display="conatuss.top"/>
-    <hyperlink ref="A3" r:id="rId3" display="droshky.fun"/>
-    <hyperlink ref="A4" r:id="rId4" display="spuddles.fun"/>
-    <hyperlink ref="A5" r:id="rId5" display="moilfuns.fun"/>
+    <hyperlink ref="A6" r:id="rId1" display="unsdgaction.com" tooltip="https://unsdgaction.com"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="1" outlineLevelCol="6"/>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="D2" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/new-info45/web.xlsx
+++ b/new-info45/web.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="14475" windowHeight="8505"/>
+    <workbookView windowWidth="14475" windowHeight="7065"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="14" r:id="rId1"/>
@@ -41,16 +41,16 @@
     <t>color2</t>
   </si>
   <si>
-    <t>amortization.site</t>
-  </si>
-  <si>
-    <t>#ffd9a3</t>
-  </si>
-  <si>
-    <t>krakenbane.com</t>
-  </si>
-  <si>
-    <t>#f597ba</t>
+    <t>read.dupioni.cloud</t>
+  </si>
+  <si>
+    <t>#4167b1</t>
+  </si>
+  <si>
+    <t>sec.dupioni.cloud</t>
+  </si>
+  <si>
+    <t>#d62828</t>
   </si>
   <si>
     <t>color1</t>
@@ -141,7 +141,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="30">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -195,6 +195,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <u/>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
@@ -430,13 +436,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFD9A3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF597BA"/>
+        <fgColor rgb="FF4167B1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD62828"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -751,148 +757,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -941,25 +947,25 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1370,7 +1376,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" ht="16.5" spans="1:8">
       <c r="A2" s="10" t="s">
         <v>3</v>
       </c>
@@ -1379,7 +1385,7 @@
       </c>
       <c r="C2" s="12"/>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" ht="16.5" spans="1:8">
       <c r="A3" s="10" t="s">
         <v>5</v>
       </c>

--- a/new-info45/web.xlsx
+++ b/new-info45/web.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="14475" windowHeight="7065"/>
+    <workbookView windowWidth="14475" windowHeight="10890"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="14" r:id="rId1"/>
@@ -41,16 +41,16 @@
     <t>color2</t>
   </si>
   <si>
-    <t>read.dupioni.cloud</t>
-  </si>
-  <si>
-    <t>#4167b1</t>
-  </si>
-  <si>
-    <t>sec.dupioni.cloud</t>
-  </si>
-  <si>
-    <t>#d62828</t>
+    <t>read.combustibly.com</t>
+  </si>
+  <si>
+    <t>#e58889</t>
+  </si>
+  <si>
+    <t>sec.combustibly.com</t>
+  </si>
+  <si>
+    <t>#b57743</t>
   </si>
   <si>
     <t>color1</t>
@@ -62,22 +62,22 @@
     <t>json</t>
   </si>
   <si>
-    <t>draconic.cloud</t>
-  </si>
-  <si>
-    <t>#e4c6d0</t>
-  </si>
-  <si>
-    <t>#425066</t>
-  </si>
-  <si>
-    <t>umbrage.cloud</t>
-  </si>
-  <si>
-    <t>#a2e2c6</t>
-  </si>
-  <si>
-    <t>#012896</t>
+    <t>play.gamelift.fun</t>
+  </si>
+  <si>
+    <t>#b0e7a4</t>
+  </si>
+  <si>
+    <t>#e63946</t>
+  </si>
+  <si>
+    <t>sec.gamelift.fun</t>
+  </si>
+  <si>
+    <t>#c2aadd</t>
+  </si>
+  <si>
+    <t>#64ffda</t>
   </si>
   <si>
     <t>haberdasher.cloud</t>
@@ -141,7 +141,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="32">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -180,6 +180,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="10"/>
       <color rgb="FF2972F4"/>
@@ -188,11 +195,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
@@ -201,9 +215,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -367,7 +380,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="45">
+  <fills count="46">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -412,25 +425,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE4C6D0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF425066"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2E2C6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF012896"/>
+        <fgColor rgb="FFB0E7A4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE63946"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC2AADD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF64FFDA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE58889"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -442,7 +461,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD62828"/>
+        <fgColor rgb="FFB57743"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -633,12 +652,21 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFE3E4E6"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -757,152 +785,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -929,43 +957,49 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1377,192 +1411,194 @@
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:8">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="12"/>
+      <c r="C2" s="18"/>
     </row>
     <row r="3" ht="16.5" spans="1:8">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="12"/>
+      <c r="C3" s="18"/>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="18"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="20"/>
+      <c r="A4" s="20"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="22"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="21"/>
-      <c r="B5" s="21"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="20"/>
+      <c r="A5" s="23"/>
+      <c r="B5" s="23"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="22"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="21"/>
-      <c r="B6" s="21"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
-      <c r="H6" s="22"/>
+      <c r="A6" s="23"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="22"/>
-      <c r="H7" s="22"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="23"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="22"/>
+      <c r="A8" s="25"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="24"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="22"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="22"/>
+      <c r="A9" s="24"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="24"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="22"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
+      <c r="A10" s="24"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="22"/>
-      <c r="B11" s="22"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
+      <c r="A11" s="24"/>
+      <c r="B11" s="24"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="24"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="22"/>
-      <c r="B12" s="22"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
+      <c r="A12" s="24"/>
+      <c r="B12" s="24"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="24"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="22"/>
-      <c r="B13" s="22"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="22"/>
+      <c r="A13" s="24"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="24"/>
+      <c r="H13" s="24"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="22"/>
-      <c r="B14" s="22"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
+      <c r="A14" s="24"/>
+      <c r="B14" s="24"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="24"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="22"/>
-      <c r="B15" s="22"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
+      <c r="A15" s="24"/>
+      <c r="B15" s="24"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="24"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="22"/>
-      <c r="B16" s="22"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="22"/>
+      <c r="A16" s="24"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="24"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="22"/>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="22"/>
+      <c r="A17" s="24"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="22"/>
-      <c r="B18" s="22"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="22"/>
+      <c r="A18" s="24"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="24"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="22"/>
-      <c r="B19" s="22"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="22"/>
-      <c r="H19" s="22"/>
+      <c r="A19" s="24"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="24"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="22"/>
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
+      <c r="A20" s="24"/>
+      <c r="B20" s="24"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
     </row>
     <row r="21" spans="1:8">
-      <c r="D21" s="22"/>
+      <c r="D21" s="24"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="F16" r:id="rId1"/>
     <hyperlink ref="F17" r:id="rId2"/>
+    <hyperlink ref="A2" r:id="rId3" display="read.combustibly.com" tooltip="http://combustibly.com"/>
+    <hyperlink ref="A3" r:id="rId3" display="sec.combustibly.com" tooltip="http://combustibly.com"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1595,7 +1631,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" ht="15" spans="1:6">
       <c r="A2" s="10" t="s">
         <v>10</v>
       </c>
@@ -1606,14 +1642,14 @@
         <v>12</v>
       </c>
       <c r="D2" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2" s="3">
         <v>6</v>
       </c>
       <c r="F2" s="3"/>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" ht="15" spans="1:6">
       <c r="A3" s="10" t="s">
         <v>13</v>
       </c>
@@ -1624,7 +1660,7 @@
         <v>15</v>
       </c>
       <c r="D3" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E3" s="3">
         <v>6</v>
